--- a/reports/一级子公司A_现金流量表_2025-05.xlsx
+++ b/reports/一级子公司A_现金流量表_2025-05.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>152646000</v>
+        <v>153082954</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>709878000</v>
+        <v>708969657</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3072651</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>14361966</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1549869</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>7168507</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>767408</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>3587750</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>619922</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2869888</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>460934</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>2150760</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>309356</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1436089</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>231083</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>1074698</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>154201</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>718333</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>386367</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1790929</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>193169</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>902382</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>123140</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>569665</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>391400</v>
+        <v>389485</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1820200</v>
+        <v>1821231</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2781000</v>
+        <v>2794806</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>12933000</v>
+        <v>12931284</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>155818400</v>
+        <v>164135345</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>98880000</v>
+        <v>98964802</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>459840000</v>
+        <v>459203246</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1025900</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>4788704</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>774088</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>3582668</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>511833</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>2393143</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>387550</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1792606</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>255835</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>1195567</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>194631</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>901696</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16171000</v>
+        <v>16119174</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>75203000</v>
+        <v>75139103</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8240000</v>
+        <v>8254937</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>38320000</v>
+        <v>38364248</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3399000</v>
+        <v>3398215</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>15807000</v>
+        <v>15785836</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>126690000</v>
+        <v>129886965</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>29128400</v>
+        <v>34248380</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>180000</v>
+        <v>179287</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>900000</v>
+        <v>899688</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1500000</v>
+        <v>1498037</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>7500000</v>
+        <v>7492074</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>920000</v>
+        <v>919724</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>4600000</v>
+        <v>4605813</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1680000</v>
+        <v>1677324</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14000000</v>
+        <v>13954397</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>70000000</v>
+        <v>70089088</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2000000</v>
+        <v>2008595</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>10000000</v>
+        <v>9989257</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10000000</v>
+        <v>9951116</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>50000000</v>
+        <v>50038179</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>380000</v>
+        <v>379117</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1900000</v>
+        <v>1898378</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14380000</v>
+        <v>14333514</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-12700000</v>
+        <v>-12656190</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3500000</v>
+        <v>3512744</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>17500000</v>
+        <v>17478621</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5500000</v>
+        <v>5527347</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>27500000</v>
+        <v>27482322</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5500000</v>
+        <v>5473158</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>27500000</v>
+        <v>27506454</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>180000</v>
+        <v>180770</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>900000</v>
+        <v>900178</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9180000</v>
+        <v>9220861</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4500000</v>
+        <v>4508287</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>22500000</v>
+        <v>22521556</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4500000</v>
+        <v>4498821</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>22500000</v>
+        <v>22472865</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>720000</v>
+        <v>719032</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>3600000</v>
+        <v>3604782</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>630000</v>
+        <v>627491</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>3150000</v>
+        <v>3153646</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>90000</v>
+        <v>90427</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>450000</v>
+        <v>449603</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5310000</v>
+        <v>5317746</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3870000</v>
+        <v>3903115</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20298400</v>
+        <v>25495305</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20298400</v>
+        <v>25495305</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
